--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>569.8</v>
+        <v>62.8</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>33.5</v>
@@ -752,13 +752,13 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -767,13 +767,13 @@
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>4.3</v>
@@ -781,23 +781,23 @@
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>10.3</v>
+      <c r="W4" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>12.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -812,22 +812,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>856143513.2</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+        <v>2.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -841,10 +847,10 @@
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>35.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>21.6</v>
+        <v>0.4</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -853,19 +859,19 @@
         <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.7</v>
+        <v>31.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>41</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.2</v>
@@ -877,10 +883,10 @@
         <v>8.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>201.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.1</v>
+        <v>80.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -895,18 +901,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>33.9</v>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="n">
-        <v>31.9</v>
+      <c r="F6" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -915,25 +927,25 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>12.2</v>
+      <c r="L6" s="8" t="n">
+        <v>488.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -942,7 +954,7 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>14.4</v>
@@ -954,10 +966,10 @@
         <v>28.9</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>16.3</v>
@@ -979,13 +991,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>583.6</v>
+        <v>53.6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>11</v>
+        <v>1.9</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>23.1</v>
@@ -994,7 +1006,7 @@
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1003,7 +1015,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1012,16 +1024,16 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
+        <v>39.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>13.8</v>
@@ -1042,10 +1054,10 @@
         <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.3</v>
@@ -1064,39 +1076,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>34.4</v>
-      </c>
+        <v>25.1</v>
+      </c>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>36.5</v>
+        <v>0.8</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1108,7 +1118,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1117,13 +1127,13 @@
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>22.1</v>
@@ -1145,19 +1155,27 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>266</v>
+        <v>2656.2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+        <v>53.3</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>111.4</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="n">
         <v>44.2</v>
       </c>
@@ -1165,48 +1183,48 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n">
-        <v>28.8</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183.8</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>165</v>
+        <v>1685</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>71.8</v>
+        <v>24.8</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.1</v>
+        <v>24.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>38.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>106.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1222,13 +1240,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>534.4</v>
+        <v>2.4</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>33.1</v>
+        <v>23.9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>18.7</v>
+        <v>1.2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.3</v>
@@ -1243,24 +1261,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>13.7</v>
+        <v>2.7</v>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="n">
-        <v>13.4</v>
+      <c r="L10" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.2</v>
+        <v>32.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>36.6</v>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
@@ -1268,28 +1284,28 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>13.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>38.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>184.1</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>150.2</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1305,10 +1321,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
+        <v>422.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
@@ -1317,13 +1333,13 @@
         <v>42.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
+        <v>41.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
@@ -1335,14 +1351,18 @@
       <c r="M11" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>0.2</v>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+8
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
@@ -1352,22 +1372,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>81</v>
+        <v>31.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>47</v>
+        <v>424</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1383,29 +1403,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 6
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 317
-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>19.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.1</v>
@@ -1414,7 +1428,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1423,7 +1437,7 @@
         <v>6.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
@@ -1431,35 +1445,37 @@
       <c r="P12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
+      <c r="Q12" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>29.2</v>
+        <v>92.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+76
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1475,13 +1491,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>601.3</v>
+        <v>61.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15.4</v>
+        <v>12.9</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
@@ -1489,7 +1505,7 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1508,19 +1524,19 @@
         <v>12.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.3</v>
+      <c r="R13" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1529,19 +1545,19 @@
         <v>13.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>28.7</v>
+        <v>49.6</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>87.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1564,7 +1580,7 @@
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1572,7 +1588,7 @@
       <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1582,43 +1598,43 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1.8</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>9.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="R14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>27</v>
+        <v>41.2</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>9.199999999999999</v>
@@ -1646,13 +1662,13 @@
       <c r="D15" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>15</v>
+      <c r="E15" s="8" t="n">
+        <v>79.5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1665,16 +1681,16 @@
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>48</v>
@@ -1685,11 +1701,11 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>14.3</v>
+      <c r="R15" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>15.4</v>
@@ -1698,7 +1714,7 @@
         <v>38</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>14</v>
@@ -1710,7 +1726,7 @@
         <v>23.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1726,16 +1742,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9572.1</v>
+        <v>2577.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1189.6</v>
+        <v>52.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>76.8</v>
+        <v>15.1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1744,29 +1760,39 @@
         <v>10.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
+14
+</t>
+        </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>822.3</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>2121.5</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>54.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>23.6</v>
@@ -1775,23 +1801,29 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>820.6</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="n">
         <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>148.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.5</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1807,74 +1839,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>26.2</v>
+        <v>0.2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>15.4</v>
+        <v>26.8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.6</v>
+        <v>2.6</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>30.9</v>
+      <c r="P17" s="8" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>60.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>7.3</v>
+        <v>72.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>96.3</v>
+        <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.1</v>
+        <v>212.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1889,63 +1921,62 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>552.1</v>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+2
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 7
-</t>
-        </is>
+        <v>34.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1.1</v>
+        <v>32.9</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>37.6</v>
+        <v>166.9</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
@@ -1960,7 +1991,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1975,13 +2006,19 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>326.4</v>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+2975
+</t>
+        </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
       </c>
@@ -1989,7 +2026,7 @@
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.8</v>
@@ -1998,7 +2035,7 @@
         <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>13.5</v>
@@ -2006,19 +2043,17 @@
       <c r="M19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R19" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2028,19 +2063,19 @@
         <v>12.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>20.4</v>
+        <v>4.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2056,15 +2091,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.3</v>
+        <v>12.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2073,34 +2113,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32</v>
+        <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2109,15 +2149,17 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41.4</v>
+        <v>4.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Y20" s="3" t="n">
         <v>32</v>
       </c>
@@ -2136,59 +2178,61 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D21" s="3" t="n"/>
+        <v>542.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>30.9</v>
+      </c>
       <c r="E21" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>492</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>2.6</v>
+        <v>12.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>26.3</v>
@@ -2203,7 +2247,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2219,16 +2263,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>516.3</v>
+        <v>536.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3.6</v>
+        <v>34.1</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22.5</v>
+        <v>43.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2237,31 +2281,31 @@
         <v>13.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J22" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>51</v>
+        <v>21.1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>30.7</v>
+        <v>22.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>4.5</v>
@@ -2270,19 +2314,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
+        <v>14.9</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>98.2</v>
+        <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2301,63 +2345,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>2547.5</v>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>16</v>
+        <v>60.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12.2</v>
+        <v>122.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>117.1</v>
+        <v>17.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>11.6</v>
+        <v>86.8</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44255
+82947
+</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="K23" s="3" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>23</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>31.3</v>
+        <v>5.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.5</v>
+        <v>30.5</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>68.8</v>
@@ -2366,9 +2414,11 @@
         <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>192.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2383,51 +2433,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5032.1</v>
+        <v>5026.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>17.4</v>
+        <v>2.8</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>78.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>50.3</v>
+        <v>5.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R24" s="8" t="n">
+      <c r="Q24" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2440,7 +2490,7 @@
         <v>87.2</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
@@ -2449,10 +2499,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2468,68 +2518,77 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.2</v>
+        <v>455.5</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>18.7</v>
+        <v>4.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>400.8</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>14.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n">
-        <v>88.8</v>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+2
+</t>
+        </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>45.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2552,35 +2611,37 @@
         <v>30.3</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>44.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n">
-        <v>10.9</v>
+        <v>72.3</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2592,25 +2653,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U26" s="8" t="n">
-        <v>2823.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>4.8</v>
+      <c r="U26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2627,30 +2688,32 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
+        <v>5.1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>82</v>
+        <v>285.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>681.6</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2658,13 +2721,13 @@
         <v>10.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>98.5</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1322</v>
+        <v>528</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>29.3</v>
@@ -2673,28 +2736,32 @@
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>28.2</v>
+        <v>3.4</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>44.3</v>
+        <v>4.2</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>20.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2713,73 +2780,77 @@
         <v>621</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>23.5</v>
+      <c r="F28" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J28" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>47</v>
+        <v>428</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>22.5</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7.2</v>
+        <v>13.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>20.8</v>
+        <v>126.5</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2795,13 +2866,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>0.6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>34.4</v>
+        <v>3.4</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>23.9</v>
@@ -2810,16 +2881,16 @@
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2828,10 +2899,10 @@
         <v>10.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>41.3</v>
+        <v>4.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2839,16 +2910,18 @@
       <c r="Q29" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>9.4</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>43.4</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>27.7</v>
       </c>
@@ -2876,73 +2949,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>624.9</v>
+        <v>0.6</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1561.6</v>
+        <v>141.6</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>29.3</v>
+        <v>2.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.9</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42</v>
+        <v>42.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>18.6</v>
+        <v>28.3</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2959,31 +3032,31 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
+        <v>556.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F31" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>18</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>522.4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>18.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -2997,21 +3070,19 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>14.2</v>
+      <c r="P31" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
@@ -3025,7 +3096,7 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3043,36 +3114,32 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>23.2</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.8</v>
@@ -3090,27 +3157,27 @@
         <v>4.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T32" s="3" t="n"/>
+        <v>4.7</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>42.4</v>
+        <v>424.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>24.6</v>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3124,14 +3191,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>31.2</v>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="8" t="n">
+        <v>444.4</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.2</v>
@@ -3140,58 +3205,58 @@
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15.8</v>
+        <v>35.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141.8</v>
+        <v>4.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>10.2</v>
+      <c r="R33" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>6.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>44.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3211,7 +3276,7 @@
         <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>14.5</v>
@@ -3226,7 +3291,7 @@
         <v>1.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3235,10 +3300,10 @@
         <v>6</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>41.2</v>
+        <v>17.2</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.8</v>
@@ -3250,13 +3315,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>2.1</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>30.3</v>
@@ -3271,13 +3336,17 @@
         <v>12.7</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>5</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+178
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3293,13 +3362,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>437.9</v>
+        <v>433.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>85.59999999999999</v>
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>23.2</v>
@@ -3308,13 +3377,13 @@
         <v>15.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>19.1</v>
+        <v>12.4</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>14.2</v>
@@ -3323,14 +3392,16 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N35" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>19</v>
@@ -3342,26 +3413,24 @@
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>10.8</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3376,10 +3445,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>222.2</v>
+        <v>22.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25.5</v>
+        <v>30.3</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>17</v>
@@ -3387,7 +3456,7 @@
       <c r="F36" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3397,10 +3466,10 @@
         <v>4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>44.2</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3408,14 +3477,12 @@
       <c r="M36" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>19.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>30.8</v>
@@ -3424,25 +3491,25 @@
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.2</v>
+        <v>21.6</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3458,57 +3525,53 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>222.2</v>
-      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
-        <v>151.6</v>
+        <v>25.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>111.2</v>
+        <v>1.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>11.2</v>
+        <v>42.4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>821.9</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>240.2</v>
+        <v>20.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>389.8</v>
+        <v>59.8</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>4.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>124.9</v>
+        <v>34.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>3.4</v>
@@ -3517,15 +3580,17 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>183.1</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>96.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3542,26 +3607,26 @@
       <c r="C38" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>20.3</v>
+      <c r="D38" s="8" t="n">
+        <v>85.59999999999999</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>10.3</v>
+        <v>16.3</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>55.8</v>
+        <v>5.8</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>301</v>
+      <c r="J38" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>36.1</v>
@@ -3570,43 +3635,43 @@
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>13.2</v>
+        <v>53.2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>4.7</v>
+        <v>47.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>14.5</v>
+        <v>33.5</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>48.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>151</v>
+        <v>11.6</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3625,39 +3690,41 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.1</v>
+        <v>5444.4</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>29.2</v>
+        <v>303.5</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F39" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>12.1</v>
+        <v>6.5</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>6000.4</v>
+      <c r="M39" s="3" t="n">
+        <v>40.6</v>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3672,25 +3739,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>20.3</v>
+        <v>0.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>29.4</v>
+        <v>2.4</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W39" s="8" t="n">
-        <v>15</v>
+      <c r="W39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3773,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
+        <v>6.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>30.3</v>
+        <v>29.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>14.2</v>
@@ -3721,28 +3788,26 @@
         <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>51.2</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="K40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.4</v>
+        <v>94.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3750,14 +3815,14 @@
       <c r="Q40" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="R40" s="8" t="n">
-        <v>15</v>
+      <c r="R40" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>822.4</v>
+        <v>22.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3769,13 +3834,13 @@
         <v>14.7</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3791,76 +3856,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>25.5</v>
+        <v>6.4</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>34.8</v>
+        <v>30.3</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>22.7</v>
+        <v>2.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>11.2</v>
+        <v>16.8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>9.5</v>
+        <v>23.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>52</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>19.5</v>
+        <v>197.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>32.6</v>
+        <v>2.6</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>828.9</v>
+        <v>28.9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>223.6</v>
+        <v>16.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3875,14 +3940,18 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>25.5</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+4811
+</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46.2</v>
+        <v>14.7</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>23.8</v>
@@ -3890,62 +3959,62 @@
       <c r="G42" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>53</v>
+      <c r="H42" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>18.3</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+      <c r="K42" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>11.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.1</v>
+        <v>45.5</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>165.5</v>
+        <v>16.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3961,76 +4030,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>324</v>
+        <v>23.9</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>9.5</v>
+        <v>98.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>58</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>76.2</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n">
-        <v>4.2</v>
+        <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>24.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>45.1</v>
+        <v>19.9</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>25.3</v>
+        <v>285.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.8</v>
+        <v>16.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4046,76 +4113,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>30.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>60.5</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G44" s="8" t="n">
-        <v>14.9</v>
+      <c r="G44" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>19.7</v>
+        <v>5.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.4</v>
+        <v>581.5</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>7.8</v>
+      <c r="R44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>89.8</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>1.4</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>8.4</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4131,13 +4198,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>231.2</v>
+        <v>58</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>185.7</v>
+        <v>30.8</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>15</v>
+        <v>150.1</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>22.9</v>
@@ -4146,61 +4213,63 @@
         <v>15.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.9</v>
+        <v>119.1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>356</v>
+        <v>6.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9</v>
+        <v>90.8</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>181.1</v>
+        <v>16.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>119.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>0.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>18.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>91.2</v>
+        <v>22.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>881.8</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>72.2</v>
+        <v>52.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>75.2</v>
+        <v>21.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>186.5</v>
+        <v>14.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>184.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>19.6</v>
+        <v>2.2</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+11
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4216,70 +4285,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>0.6</v>
+        <v>232.2</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>87.7</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>139.9</v>
+        <v>232.1</v>
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>35</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
+        <v>524.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>26.5</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>92</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>332.1</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>30.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>24.8</v>
+        <v>751.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>14.4</v>
+        <v>18.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>10.8</v>
+        <v>64.8</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>19.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,69 +736,57 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>62.8</v>
+        <v>1569.8</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n">
-        <v>2.8</v>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>13.2</v>
+      <c r="Q4" s="8" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -812,33 +800,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>512.7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>2.8</v>
+      <c r="G5" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>12.9</v>
+        <v>44.2</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.8</v>
@@ -846,47 +830,45 @@
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>35.5</v>
+      <c r="M5" s="8" t="n">
+        <v>65.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>14.2</v>
+        <v>5.7</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="8" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>8.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>21.2</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>80.8</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -901,24 +883,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>1504.8</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>32.1</v>
+        <v>34.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="8" t="n">
+        <v>20623.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -927,55 +905,53 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>488.7</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>8.4</v>
+        <v>16</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>89.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42.4</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16.3</v>
+        <v>201.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>3.3</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -991,76 +967,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>53.6</v>
+        <v>583.6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I7" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>46.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>54.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>51.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>12.2</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.3</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1076,37 +1050,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>26.5</v>
+        <v>236.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1114,32 +1088,32 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>7.9</v>
+      <c r="S8" s="8" t="n">
+        <v>71</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U8" s="8" t="n">
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>1.7</v>
+        <v>45.1</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>22.1</v>
+        <v>86.7</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>34.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1155,76 +1129,72 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2656.2</v>
+        <v>2636</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>61.1</v>
+        <v>1169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>111.4</v>
-      </c>
+        <v>23.3</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2262
-411464141
-</t>
-        </is>
+        <v>116.4</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.2</v>
+        <v>1644.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M9" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>2.8</v>
+        <v>258.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>949.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1685</v>
+        <v>1169</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
+        <v>71.8</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>127.7</v>
+      </c>
       <c r="T9" s="3" t="n">
-        <v>55.9</v>
+        <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.1</v>
+        <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>139.7</v>
+        <v>1139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.6</v>
+        <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>38.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>16.2</v>
+        <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90.2</v>
+        <v>1120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1240,72 +1210,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.4</v>
+        <v>231.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1.2</v>
+        <v>331.6</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10.7</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>32.6</v>
+        <v>16.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="P10" s="3" t="n"/>
+        <v>236.6</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>99.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U10" s="8" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>2.9</v>
+      <c r="V10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>38.2</v>
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0.8</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>184.1</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>11.2</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1321,75 +1293,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>422.9</v>
+        <v>1427.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17.2</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>42.1</v>
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.1</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="8" t="n">
+        <v>148.9</v>
+      </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1404,78 +1364,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>11.9</v>
+        <v>206.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31.7</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>21.7</v>
+        <v>44.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>28.7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>31.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6.8</v>
+        <v>16.2</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-76
-</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1491,75 +1447,75 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>61.3</v>
+        <v>1601.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>11.8</v>
+      <c r="H13" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>11.7</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>1249</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>87.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>28.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>7.1</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>1265.4</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1574,22 +1530,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
+        <v>1488</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F14" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>11.4</v>
+      <c r="H14" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8.1</v>
@@ -1598,51 +1554,45 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>4.4</v>
+        <v>161.1</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>431.2</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1657,76 +1607,68 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.4</v>
+        <v>1832.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>34.3</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.8</v>
+        <v>92.8</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>22.1</v>
-      </c>
+        <v>115.4</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>23.4</v>
+        <v>123.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1742,88 +1684,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2577.7</v>
+        <v>0.9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>52.6</v>
+        <v>1291.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15.1</v>
+        <v>2726.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.2</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>35.3</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-14
-</t>
-        </is>
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>189.9</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2952.9</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>2121.5</v>
+        <v>2212</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>54.7</v>
+        <v>1154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.6</v>
+        <v>1083.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>820.6</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-7918949
-</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>1131</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>48.3</v>
+        <v>148.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>148.8</v>
+        <v>11245.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>19.1</v>
+        <v>1124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1839,75 +1767,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2</v>
+        <v>315.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.2</v>
+        <v>31.9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2.6</v>
+        <v>15.4</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>6.8</v>
+        <v>16</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.7</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N17" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>60.9</v>
+        <v>942.5</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>72.3</v>
+        <v>4.7</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>87.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
+        <v>37.6</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>212.1</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>44.9</v>
-      </c>
+        <v>229.2</v>
+      </c>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1921,77 +1845,73 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
-2
-</t>
-        </is>
+      <c r="C18" s="3" t="n">
+        <v>532.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" s="3" t="n"/>
+        <v>2.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G18" s="3" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>5.9</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>911.1</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.9</v>
+        <v>115.5</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>14.4</v>
+        <v>40.4</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="8" t="n">
+        <v>184.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2006,18 +1926,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-2975
-</t>
-        </is>
+      <c r="C19" s="3" t="n">
+        <v>326.4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>12.9</v>
+        <v>33.4</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -2026,29 +1942,27 @@
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>60.8</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
@@ -2057,27 +1971,27 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>96.2</v>
-      </c>
+        <v>112.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr"/>
       <c r="W19" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2091,56 +2005,51 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.3</v>
+      <c r="C20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="8" t="n">
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L20" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5</v>
+        <v>522</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>10.6</v>
+      <c r="R20" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2149,21 +2058,23 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>12.4</v>
+        <v>29.8</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>182.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2181,42 +2092,40 @@
         <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>1.1</v>
+        <v>30.2</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>36.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>1.6</v>
+        <v>13.2</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>12.7</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2226,28 +2135,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1.6</v>
+        <v>17.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2263,75 +2172,75 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
+        <v>1536.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.1</v>
+        <v>34.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>13.3</v>
+      <c r="H22" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M22" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>21.1</v>
+        <v>51</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>216.3</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>126.2</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2345,79 +2254,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="n">
+        <v>231.5</v>
+      </c>
       <c r="D23" s="3" t="n">
-        <v>60.3</v>
+        <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>122.4</v>
+        <v>72.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17.1</v>
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44255
-82947
-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.2</v>
+        <v>719.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.1</v>
+        <v>20.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>23</v>
+        <v>1212</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.4</v>
+        <v>141.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.4</v>
+        <v>154.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>4.9</v>
+        <v>182.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>292</v>
+        <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>30.5</v>
+        <v>1302.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>68.8</v>
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>17.3</v>
+        <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>192.1</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2433,76 +2340,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5026.1</v>
+        <v>309.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.8</v>
+        <v>14.7</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>78.40000000000001</v>
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>54.6</v>
+        <v>4.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>87.2</v>
+        <v>116.6</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>37.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2518,79 +2421,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
+        <v>425.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>12.2</v>
+        <v>43.2</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>11.8</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>14</v>
+        <v>140</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>114</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-2
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-171111
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
+        <v>911.1</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>1457.5</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1112.1</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2610,70 +2507,68 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>24.8</v>
+      <c r="E26" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>22.5</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>15</v>
+      <c r="H26" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L26" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.8</v>
+        <v>33.4</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>26.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>227</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2688,80 +2583,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.1</v>
+        <v>550.1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>14.8</v>
+        <v>3.1</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>285.8</v>
+        <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>98.5</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>528</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>29.3</v>
+        <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>7.1</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>3.4</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>37.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>1026.6</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2777,80 +2660,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>621</v>
+        <v>1621</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>6.5</v>
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>28.1</v>
+        <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>1.8</v>
+      <c r="M28" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.8</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>1428</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>120.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>30.8</v>
+        <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>166</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="V28" s="8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.9</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
+        <v>18.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2866,75 +2745,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.6</v>
+        <v>624.9</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>4.6</v>
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>12.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>23.9</v>
+        <v>29.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20.4</v>
+        <v>17.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.3</v>
+        <v>141.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4.6</v>
+        <v>45.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n">
+        <v>3068.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2949,75 +2828,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>141.6</v>
+        <v>161.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>12.2</v>
+        <v>714.5</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.3</v>
+        <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.1</v>
+        <v>187.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.5</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>55.8</v>
+        <v>155.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>110.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.3</v>
+        <v>130.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.3</v>
+        <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>33.5</v>
+        <v>153.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>8194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>6.8</v>
+        <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3032,71 +2907,65 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>556.4</v>
+        <v>236.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>4.5</v>
+        <v>48.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>18</v>
+        <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4</v>
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>11.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J31" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>43.1</v>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>155.1</v>
+        <v>31</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="n">
+        <v>114.5</v>
+      </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W31" s="3" t="n">
+      <c r="V31" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.5</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3114,70 +2983,68 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>424.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>17.1</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="n">
+        <v>31.9</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3191,74 +3058,72 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="8" t="n">
-        <v>444.4</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="C33" s="3" t="n">
+        <v>448.7</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>35.8</v>
+        <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>5.7</v>
+      <c r="M33" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="R33" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="8" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="8" t="n">
+        <v>218</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3276,77 +3141,69 @@
         <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>1.1</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>6</v>
+        <v>14.2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0.8</v>
+      <c r="M34" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>116</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>12952.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>30.3</v>
+        <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+      <c r="X34" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-178
-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3365,61 +3222,57 @@
         <v>433.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>12.4</v>
+        <v>30.3</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>14.2</v>
+        <v>5.3</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>2.1</v>
+        <v>124</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>55</v>
+        <v>222.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
@@ -3428,9 +3281,11 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>1839.8</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>422.1</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3445,73 +3300,71 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>22.2</v>
+        <v>341.3</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>30.3</v>
+        <v>25.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>23.7</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="n">
-        <v>9.1</v>
+        <v>21.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="M36" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>22.8</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>21.6</v>
+        <v>0.1</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>218.8</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>116.8</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3525,71 +3378,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>966.1</v>
+      </c>
       <c r="D37" s="3" t="n">
-        <v>25.5</v>
+        <v>1181.6</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.9</v>
+        <v>168.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>18.5</v>
+        <v>1110.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.2</v>
+        <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>42.4</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>101</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>36.4</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>821.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>123.2</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>20.2</v>
+        <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.8</v>
+        <v>594.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>24.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.2</v>
+        <v>1782.6</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>4.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>34.1</v>
+        <v>1141</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.4</v>
+        <v>1134.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>79</v>
+        <v>0.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>49.2</v>
+        <v>949.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>183.1</v>
+        <v>181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>96.2</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3605,73 +3464,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>85.59999999999999</v>
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>42.8</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>16.3</v>
+        <v>22.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>111.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>36.1</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>47.8</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>1418</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>59.8</v>
+        <v>16.9</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>33.5</v>
+        <v>26.7</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>48.5</v>
+        <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>9.5</v>
+        <v>940.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>28.9</v>
+        <v>30.8</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>37.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3690,47 +3545,45 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.4</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>303.5</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>6.5</v>
+        <v>314.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>15.5</v>
@@ -3739,25 +3592,23 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.4</v>
+        <v>396.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>22.2</v>
+        <v>226.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3773,74 +3624,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.4</v>
+        <v>617.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>29.2</v>
+        <v>30.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>51.2</v>
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>26221.7</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.2</v>
+        <v>18.3</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>16.2</v>
+      </c>
       <c r="M40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>94.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>15.5</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>1.1</v>
+        <v>19</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="8" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>21</v>
+        <v>8120.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.6</v>
+        <v>1221.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3856,76 +3707,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>6.4</v>
+        <v>587.5</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>14.7</v>
+        <v>340.1</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>16.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.7</v>
+        <v>23.8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5.6</v>
+        <v>16.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>18.8</v>
+        <v>49</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>15</v>
+        <v>29.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>15.3</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>26</v>
+        <v>122.2</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>28.9</v>
+        <v>128.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3940,81 +3789,75 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-4811
-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E42" s="3" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="n">
+        <v>920.9</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="R42" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>2.6</v>
+        <v>28.1</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>5.8</v>
+        <v>192.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4030,74 +3873,72 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>23.9</v>
+        <v>354</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>14.2</v>
+      <c r="F43" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>98.5</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>9.9</v>
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>28.7</v>
+        <v>201.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>24.6</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>41.8</v>
+        <v>13.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>285.3</v>
+        <v>1925.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>16.5</v>
+        <v>246.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4113,76 +3954,72 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>23.5</v>
+        <v>238</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>17.7</v>
+        <v>15.7</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>16.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>581.5</v>
+        <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>89.8</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>21.8</v>
+        <v>109.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>1.4</v>
+        <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>8.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.6</v>
+        <v>182.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4198,78 +4035,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>58</v>
+        <v>33102.9</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>30.8</v>
+        <v>11871.5</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>150.1</v>
+        <v>191.9</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>22.9</v>
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>15.7</v>
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>119.1</v>
+        <v>11.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>6.1</v>
+        <v>82224.60000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>90.8</v>
+        <v>1512.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>3.5</v>
+        <v>1822.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.6</v>
+        <v>111011.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
+        <v>1815.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>0.4</v>
+        <v>11226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>22.2</v>
+        <v>133.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S45" s="3" t="n"/>
+        <v>1021.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>183.8</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>2.2</v>
+        <v>1836.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>52.8</v>
+        <v>8888.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.2</v>
+        <v>21462.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>14.7</v>
+        <v>106.1</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>1098.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-11
-</t>
-        </is>
+        <v>1222.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1117.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4285,68 +4118,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>232.2</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>87.7</v>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.9</v>
+        <v>18.3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="I46" s="3" t="n">
-        <v>35</v>
+        <v>6.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>524.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>8.6</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="n">
-        <v>26.5</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="R46" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>751.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>64.8</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,47 +736,55 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1569.8</v>
+        <v>562.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="8" t="n">
-        <v>72.8</v>
+      <c r="H4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>38.3</v>
+      <c r="Q4" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -801,74 +809,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
+        <v>15127.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="E5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>21.8</v>
+      <c r="G5" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>44.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>65.5</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="8" t="n">
+      <c r="T5" s="3" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="8" t="n">
-        <v>10.3</v>
+      <c r="W5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>32.2</v>
+        <v>38.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -884,10 +894,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1504.8</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>34.8</v>
+        <v>2304.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>33.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
@@ -895,8 +905,8 @@
       <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>20623.1</v>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -908,25 +918,27 @@
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>89.8</v>
+        <v>6</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1140</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="8" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -936,22 +948,22 @@
         <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>14.2</v>
+      <c r="W6" s="8" t="n">
+        <v>64.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>201.2</v>
+        <v>20.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -975,10 +987,10 @@
       <c r="E7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -988,53 +1000,55 @@
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>8</v>
+        <v>16.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>22.1</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>8.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v>42.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>13.5</v>
+        <v>29.1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.4</v>
+        <v>23.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1050,37 +1064,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>485.1</v>
+        <v>11285.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>151</v>
+        <v>24.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>81.2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2</v>
+        <v>11</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>29.9</v>
+        <v>19.1</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>236.5</v>
+        <v>36</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1091,30 +1109,28 @@
       <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="8" t="n">
-        <v>71</v>
+      <c r="S8" s="3" t="n">
+        <v>87</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>45.1</v>
+      <c r="V8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="W8" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="X8" s="8" t="n">
-        <v>11.7</v>
+      <c r="X8" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>11098.2</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1129,51 +1145,55 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636</v>
+        <v>2666</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1169.7</v>
+        <v>169.7</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
+        <v>1413.4</v>
+      </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>39.1</v>
+        <v>329.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1644.2</v>
+        <v>614.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
+        <v>32.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>258.7</v>
+        <v>121.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>949.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1169</v>
+        <v>169</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
@@ -1182,7 +1202,7 @@
         <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1139.7</v>
+        <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>169.6</v>
@@ -1194,7 +1214,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1120.2</v>
+        <v>1158.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1213,71 +1233,69 @@
         <v>231.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>331.6</v>
+        <v>22.9</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>10.7</v>
+        <v>87.2</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
+        <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>99.8</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V10" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>17.8</v>
+      <c r="X10" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>99.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1293,33 +1311,37 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1427.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+        <v>427.9</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="F11" s="3" t="n">
-        <v>23.9</v>
+        <v>83.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.6</v>
+        <v>13.9</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>11.7</v>
+      </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16.4</v>
+        <v>61.4</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
@@ -1328,24 +1350,22 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>148.9</v>
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>122</v>
+        <v>822</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>21.7</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1364,29 +1384,31 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.1</v>
+        <v>206.7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>31.7</v>
+        <v>51.7</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>44.8</v>
+        <v>14.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>28.7</v>
+        <v>21.7</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n">
+        <v>6.1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1395,22 +1417,22 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.6</v>
+        <v>53</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16.2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
@@ -1419,19 +1441,19 @@
         <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
+        <v>21.7</v>
       </c>
       <c r="W12" s="8" t="n">
         <v>84</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>47</v>
+        <v>1217</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>4.8</v>
+        <v>1835.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1447,19 +1469,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1601.3</v>
+        <v>601.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F13" s="8" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>18.9</v>
+      <c r="G13" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>11.4</v>
@@ -1467,11 +1489,11 @@
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
@@ -1481,40 +1503,40 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>1249</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>13.8</v>
+      <c r="R13" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1265.4</v>
+        <v>86.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1530,21 +1552,21 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F14" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G14" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1562,36 +1584,44 @@
       <c r="M14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="P14" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>7.3</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>161.1</v>
-      </c>
-      <c r="U14" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="V14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>431.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1607,69 +1637,73 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1832.9</v>
+        <v>252.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>23.1</v>
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>93.3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>16.3</v>
+        <v>16.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T15" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="n">
+        <v>820.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
-        <v>123.4</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1684,22 +1718,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9</v>
+        <v>237.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1291.6</v>
+        <v>182391.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2726.8</v>
+        <v>216.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>97.3</v>
@@ -1708,15 +1742,17 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>10.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>189.9</v>
+        <v>189.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2952.9</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>202.8</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="O16" s="3" t="n">
         <v>2212</v>
       </c>
@@ -1724,10 +1760,10 @@
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1154.7</v>
+        <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1083.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
@@ -1736,22 +1772,22 @@
         <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1188.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1131</v>
+        <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>172.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>148.3</v>
+        <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>11245.8</v>
+        <v>1143.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1124.4</v>
+        <v>1024.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1769,19 +1805,19 @@
       <c r="C17" s="3" t="n">
         <v>315.4</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>31.9</v>
+      <c r="D17" s="8" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>23.6</v>
+        <v>231.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
@@ -1791,15 +1827,17 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>942.5</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1808,19 +1846,19 @@
         <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>87.3</v>
+        <v>14.7</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>37.6</v>
+        <v>116.4</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>81.59999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>26.3</v>
+        <v>946.5</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>14.5</v>
@@ -1829,9 +1867,11 @@
         <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>229.2</v>
-      </c>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1846,72 +1886,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>532.1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>12.4</v>
+        <v>1032.1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>22.7</v>
+        <v>82.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>15.2</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="3" t="inlineStr"/>
+      <c r="V18" s="8" t="n">
+        <v>8.1</v>
+      </c>
       <c r="W18" s="8" t="n">
-        <v>184.4</v>
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1927,13 +1971,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>596.5</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>12.3</v>
+        <v>35.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -1948,49 +1992,55 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>120.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr"/>
+        <v>61.4</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2006,49 +2056,51 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="8" t="n">
+        <v>9390.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>522</v>
+        <v>25</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2061,19 +2113,19 @@
         <v>29.8</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>22.2</v>
+        <v>620.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>182.4</v>
+        <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>28.7</v>
+        <v>118.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2089,43 +2141,45 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.2</v>
+        <v>942.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G21" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="H21" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>77.5</v>
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>10.5</v>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2135,28 +2189,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>14.5</v>
+        <v>86.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>217.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2172,21 +2226,21 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1536.3</v>
+        <v>536.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.8</v>
+        <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>222.5</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2195,16 +2249,18 @@
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="8" t="n">
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
       </c>
@@ -2212,34 +2268,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>24.3</v>
+        <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U22" s="8" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>216.3</v>
+        <v>26.3</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2255,22 +2311,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>231.5</v>
+        <v>2517.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>160.3</v>
+        <v>160.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>72.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1117.1</v>
+        <v>13.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>86.8</v>
+        <v>186.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2282,49 +2338,49 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>719.1</v>
+        <v>1.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1212</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>141.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>154.4</v>
+        <v>134.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>13.5</v>
+        <v>73.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>36.6</v>
+        <v>56.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1302.6</v>
+        <v>138.8</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>1127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2340,13 +2396,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>309.5</v>
+        <v>543.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>32.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>23.4</v>
@@ -2354,33 +2410,37 @@
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>4.6</v>
+        <v>34.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2395,17 +2455,15 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="W24" s="3" t="inlineStr"/>
       <c r="X24" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2421,25 +2479,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>11.9</v>
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>43.2</v>
+        <v>17.7</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.9</v>
@@ -2447,34 +2505,38 @@
       <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="M25" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>911.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>87.3</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>120.2</v>
+        <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>17.7</v>
+        <v>42.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>7.7</v>
       </c>
       <c r="W25" s="8" t="n">
         <v>11</v>
@@ -2483,10 +2545,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1457.5</v>
+        <v>1411.4</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>21821828</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2502,53 +2564,55 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>530.4</v>
+        <v>230.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>15.5</v>
+      <c r="F26" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>5.5</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>11.6</v>
+        <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>182</v>
+        <v>812</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.1</v>
+        <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>18</v>
@@ -2556,18 +2620,20 @@
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Y26" s="3" t="n">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>125</v>
+        <v>25.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2586,34 +2652,38 @@
         <v>550.1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E27" s="8" t="n">
+        <v>311.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>23.5</v>
+        <v>235.6</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>16.6</v>
+        <v>26.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
-        <v>10.6</v>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>16.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>22</v>
       </c>
@@ -2624,27 +2694,29 @@
         <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="T27" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>37.4</v>
+      <c r="U27" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>1026.6</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>1865.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2660,21 +2732,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
+        <v>631</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F28" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>464.6</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H28" s="3" t="n">
+      <c r="G28" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2684,37 +2756,37 @@
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1428</v>
+        <v>142</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>120.8</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.3</v>
+        <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>43.4</v>
+        <v>28.4</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2729,7 +2801,7 @@
         <v>18.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>30.8</v>
+        <v>90.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2745,62 +2817,64 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>624.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>34.4</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>12.2</v>
+        <v>22.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>0.8</v>
+        <v>49.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>141.3</v>
+        <v>4.1</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Q29" s="8" t="n">
-        <v>83.5</v>
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.6</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>42.1</v>
+      </c>
       <c r="V29" s="8" t="n">
-        <v>27.7</v>
+        <v>75.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
@@ -2809,10 +2883,10 @@
         <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>18.6</v>
+        <v>118.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>3068.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2828,40 +2902,40 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
+        <v>2181.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>161.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>714.5</v>
+        <v>726.5</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>187.1</v>
+        <v>181.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>372</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>155.8</v>
+        <v>139.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>110.9</v>
+        <v>118.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>130.6</v>
+        <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>222.3</v>
@@ -2870,17 +2944,19 @@
         <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>159.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="S30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>8194.1</v>
+        <v>1194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -2889,10 +2965,14 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>1190</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>42.9</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2907,19 +2987,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
+        <v>856.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>48.9</v>
+        <v>14.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>17.4</v>
+        <v>4.8</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -2930,12 +3010,18 @@
       <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
@@ -2945,27 +3031,29 @@
       <c r="Q31" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="S31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T31" s="3" t="n">
-        <v>114.5</v>
+        <v>14.5</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W31" s="8" t="n">
+      <c r="V31" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -2984,66 +3072,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>33.8</v>
+        <v>6144.4</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="8" t="n">
-        <v>1232.1</v>
+      <c r="G32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.6</v>
+        <v>62.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>94.2</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>126</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="T32" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="8" t="n">
+      <c r="U32" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3059,13 +3157,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>448.7</v>
+        <v>613.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>14.8</v>
+        <v>31.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>22.9</v>
@@ -3083,46 +3181,50 @@
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
+        <v>20.1</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="T33" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="U33" s="3" t="inlineStr"/>
+        <v>30.2</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
       <c r="V33" s="8" t="n">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>13.5</v>
+        <v>61.7</v>
       </c>
       <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>10.2</v>
+        <v>1455.4</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>1.3</v>
+        <v>103.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3138,21 +3240,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>386.6</v>
+        <v>3846.3</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F34" s="8" t="n">
+      <c r="E34" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3160,50 +3266,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>116</v>
+      <c r="N34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>12952.2</v>
+        <v>42.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>13.4</v>
+        <v>32.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="X34" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>11.6</v>
+        <v>1860.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3219,29 +3325,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>433.9</v>
+        <v>439.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>30.3</v>
+        <v>50.3</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="8" t="n">
+      <c r="F35" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>28.5</v>
+        <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3249,42 +3357,44 @@
       <c r="M35" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>19.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>222.8</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1839.8</v>
+        <v>23</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>422.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3305,65 +3415,69 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="n">
+        <v>18.7</v>
+      </c>
       <c r="G36" s="3" t="n">
-        <v>14.3</v>
+        <v>26.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J36" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L36" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>822.1</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>218.8</v>
+        <v>1498.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3379,76 +3493,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>966.1</v>
+        <v>2216.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1181.6</v>
+        <v>121.6</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>168.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1110.2</v>
+        <v>11025.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>15.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>101</v>
+        <v>1018</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>36.4</v>
+        <v>8.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>123.2</v>
+        <v>23.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>594.1</v>
+        <v>593.5</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.5</v>
+        <v>133.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1782.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1141</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1134.2</v>
+        <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>114.1</v>
+        <v>111.3</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0.6</v>
+        <v>87</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>949.8</v>
+        <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
+        <v>1315</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3464,57 +3578,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>443.3</v>
+        <v>473.3</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>20.2</v>
+        <v>30.3</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>111.2</v>
+        <v>19.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>1418</v>
+        <v>18</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>940.1</v>
+        <v>12.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>26.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3545,48 +3663,52 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>314.6</v>
+        <v>914.6</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>29.2</v>
+        <v>192.1</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>14.2</v>
+        <v>1412.6</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>21.7</v>
+        <v>211.9</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>51.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>13.2</v>
+        <v>510.1</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>15.5</v>
+        <v>211</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>59.3</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
@@ -3594,21 +3716,23 @@
       <c r="T39" s="3" t="n">
         <v>122.4</v>
       </c>
-      <c r="U39" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="8" t="n">
+      <c r="U39" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>226.6</v>
+        <v>28.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3624,31 +3748,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
+        <v>6471.6</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>30.3</v>
+        <v>91.7</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>4.3</v>
+        <v>14.7</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>26221.7</v>
+        <v>22.7</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>8.6</v>
+      <c r="I40" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>16.2</v>
@@ -3657,7 +3781,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3668,30 +3792,32 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="V40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="W40" s="8" t="n">
         <v>84.7</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>10.1</v>
+        <v>16.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>8120.6</v>
+        <v>38</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1221.6</v>
+        <v>2216.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3710,16 +3836,16 @@
         <v>587.5</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>340.1</v>
+        <v>314.1</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>16.2</v>
+        <v>62.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>15.2</v>
+      <c r="G41" s="8" t="n">
+        <v>1662.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
@@ -3731,51 +3857,51 @@
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>10.1</v>
+      </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>15.3</v>
+      <c r="R41" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="V41" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>10.1</v>
+      <c r="X41" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1828.4</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3792,29 +3918,29 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>313.1</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>23.3</v>
+      <c r="D42" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>16.8</v>
@@ -3822,43 +3948,43 @@
       <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>920.9</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="R42" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3873,16 +3999,16 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>30.5</v>
+        <v>254</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>5.6</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>23.9</v>
+      <c r="F43" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>4.1</v>
@@ -3891,54 +4017,58 @@
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="M43" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="8" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>201.3</v>
+        <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22.7</v>
+        <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1925.3</v>
+        <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>246.1</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3954,7 +4084,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.7</v>
@@ -3963,24 +4093,28 @@
         <v>15</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>22.9</v>
+        <v>222.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="8" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="8" t="n">
+      <c r="H44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>2.8</v>
+        <v>19.8</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3989,22 +4123,22 @@
         <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q44" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R44" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>109.3</v>
+        <v>119.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>12.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
@@ -4013,13 +4147,13 @@
         <v>14.7</v>
       </c>
       <c r="X44" s="8" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>182.4</v>
+        <v>1122.1</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4034,76 +4168,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>33102.9</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>11871.5</v>
+        <v>1555.1</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>191.9</v>
+        <v>411.9</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1122.1</v>
+        <v>1102.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>21</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.2</v>
+        <v>29.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82224.60000000001</v>
+        <v>345</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1512.3</v>
+        <v>226.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1822.2</v>
+        <v>14.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111011.1</v>
+        <v>1291.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1815.9</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>11226.5</v>
+        <v>102261.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
+        <v>920.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>133.4</v>
+        <v>128.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1021.8</v>
+        <v>11.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>183.8</v>
+        <v>182</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1836.9</v>
+        <v>126.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>8888.6</v>
+        <v>102.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21462.1</v>
+        <v>141.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>106.1</v>
+        <v>101</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1098.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.8</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>1117.2</v>
-      </c>
+        <v>1222.4</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4121,62 +4253,68 @@
         <v>551.8</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>119.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>119.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>562.8</v>
+        <v>569.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>21.6</v>
@@ -751,7 +751,7 @@
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -766,10 +766,10 @@
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>34.5</v>
@@ -778,9 +778,9 @@
         <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R4" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -809,40 +809,40 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15127.1</v>
+        <v>648.3</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>10</v>
+      <c r="E5" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22.2</v>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -860,10 +860,10 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>444.9</v>
+        <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
@@ -875,10 +875,10 @@
         <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2304.8</v>
+        <v>306.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>33.9</v>
@@ -902,35 +902,35 @@
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.8</v>
+        <v>2.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>2109.8</v>
+        <v>100.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>8.5</v>
@@ -942,28 +942,28 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>41.8</v>
+      <c r="U6" s="8" t="n">
+        <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="8" t="n">
-        <v>64.2</v>
+      <c r="W6" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>20.2</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -994,25 +994,25 @@
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1021,34 +1021,34 @@
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>1.7</v>
+        <v>21.7</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.5</v>
+        <v>86.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>23.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>11285.1</v>
+        <v>285.1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
@@ -1072,8 +1072,8 @@
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>82.8</v>
+      <c r="F8" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>23.4</v>
@@ -1082,23 +1082,23 @@
         <v>11.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>81.2</v>
+        <v>0.4</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>16.1</v>
+      <c r="K8" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36</v>
+        <v>3262</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1110,7 +1110,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1118,17 +1118,17 @@
       <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W8" s="8" t="n">
+      <c r="V8" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>11098.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1145,37 +1145,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2666</v>
+        <v>19656.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>169.7</v>
+        <v>1169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1413.4</v>
-      </c>
+        <v>38.3</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>329.1</v>
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>614.2</v>
+        <v>14.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>121.7</v>
@@ -1184,7 +1182,7 @@
         <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>169</v>
@@ -1214,7 +1212,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1158.4</v>
+        <v>120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1230,22 +1228,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>231.2</v>
+        <v>531.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>87.2</v>
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1265,7 +1263,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
@@ -1274,13 +1272,13 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="8" t="n">
-        <v>94.8</v>
+      <c r="U10" s="3" t="n">
+        <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.9</v>
@@ -1288,11 +1286,11 @@
       <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>99.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8</v>
@@ -1313,37 +1311,39 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>8</v>
+      <c r="D11" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>83.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H11" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>113</v>
       </c>
@@ -1353,17 +1353,17 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>14.9</v>
+      <c r="R11" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>822</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
@@ -1387,15 +1387,13 @@
         <v>206.7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>14.8</v>
-      </c>
+        <v>51.3</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1426,19 +1424,19 @@
         <v>10</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.7</v>
@@ -1447,13 +1445,13 @@
         <v>84</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>12.9</v>
+        <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1217</v>
+        <v>1417</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>1835.8</v>
+        <v>18.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1474,20 +1472,18 @@
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>59.4</v>
+      <c r="E13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="G13" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
@@ -1503,7 +1499,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>849</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
@@ -1512,7 +1508,7 @@
         <v>33.2</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1526,17 +1522,17 @@
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="8" t="n">
-        <v>2.1</v>
+      <c r="X13" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>86.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1558,13 +1554,13 @@
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>24.4</v>
+      <c r="G14" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13.6</v>
@@ -1576,16 +1572,16 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>49</v>
@@ -1597,10 +1593,10 @@
         <v>30.3</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>73.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
@@ -1614,14 +1610,14 @@
       <c r="W14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="X14" s="8" t="n">
-        <v>81.2</v>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>80.8</v>
+        <v>1020.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.2</v>
+        <v>231.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1637,19 +1633,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>252.1</v>
+        <v>2652.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>93.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
@@ -1666,41 +1662,39 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4.8</v>
+        <v>148.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>820.8</v>
+        <v>15.4</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" s="3" t="inlineStr"/>
       <c r="Z15" s="3" t="inlineStr"/>
@@ -1718,16 +1712,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.1</v>
+        <v>257.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>182391.6</v>
+        <v>8291.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>216.8</v>
+        <v>21.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>118.2</v>
+        <v>1118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1742,25 +1736,23 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>189.8</v>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="n">
-        <v>202.8</v>
+        <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212</v>
+        <v>2212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>184.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1769,22 +1761,22 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>188.2</v>
+        <v>128.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>172.8</v>
+        <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1143.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1024.4</v>
@@ -1803,19 +1795,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>2313.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>231.6</v>
+        <v>24.4</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1826,18 +1818,20 @@
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1849,13 +1843,13 @@
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>81.59999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>946.5</v>
@@ -1870,7 +1864,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>24.9</v>
+        <v>29.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1886,28 +1880,26 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1032.1</v>
+        <v>232.1</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7.4</v>
+        <v>0.1</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>82.7</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1919,7 +1911,7 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
@@ -1928,34 +1920,34 @@
         <v>6.6</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.5</v>
+        <v>118.3</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>8.1</v>
+        <v>28.1</v>
       </c>
       <c r="W18" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1971,13 +1963,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.5</v>
+        <v>596.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.4</v>
+        <v>33.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.3</v>
+        <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -1988,23 +1980,21 @@
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>120.6</v>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.5</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>17.1</v>
+        <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>60.5</v>
@@ -2019,16 +2009,16 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>61.4</v>
+      <c r="U19" s="3" t="n">
+        <v>41.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
@@ -2037,10 +2027,10 @@
         <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2056,13 +2046,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9390.5</v>
+        <v>322.8</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11.8</v>
+        <v>3.1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>17.2</v>
+        <v>4.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
@@ -2070,29 +2060,29 @@
       <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>11.1</v>
+      <c r="N20" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2107,22 +2097,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.5</v>
+        <v>44.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="8" t="n">
-        <v>620.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2141,16 +2131,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>942.2</v>
+        <v>42.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>16.4</v>
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>14.5</v>
@@ -2159,7 +2149,7 @@
         <v>11.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>10.6</v>
@@ -2167,8 +2157,8 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>17.7</v>
+      <c r="L21" s="8" t="n">
+        <v>75.7</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>11.5</v>
@@ -2201,16 +2191,16 @@
         <v>86.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>217.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2216,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
+        <v>936.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
@@ -2234,8 +2224,8 @@
       <c r="E22" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>12.5</v>
+      <c r="F22" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2259,7 +2249,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
@@ -2277,19 +2267,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="8" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>14.6</v>
+      <c r="W22" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2314,19 +2304,19 @@
         <v>2517.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>160.5</v>
+        <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>13.1</v>
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>186.8</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2338,28 +2328,28 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>4.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>1272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>134.4</v>
+        <v>254.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.5</v>
+        <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>56.6</v>
+        <v>368.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2368,10 +2358,10 @@
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.8</v>
+        <v>138.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>42.8</v>
@@ -2380,7 +2370,7 @@
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1127.4</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2396,49 +2386,47 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>543.5</v>
+        <v>503.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J24" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>10.1</v>
+        <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.6</v>
+        <v>24.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.9</v>
+        <v>20.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>14.7</v>
@@ -2447,7 +2435,7 @@
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>37.4</v>
@@ -2455,15 +2443,17 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2509,46 +2499,46 @@
         <v>19.8</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>21.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>401</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>4.2</v>
+        <v>29.4</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>87.3</v>
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42.8</v>
+        <v>12.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1411.4</v>
+        <v>41.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>21821828</v>
+        <v>1112.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2564,7 +2554,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>230.4</v>
+        <v>530.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.3</v>
@@ -2575,8 +2565,8 @@
       <c r="F26" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>5.5</v>
+      <c r="G26" s="3" t="n">
+        <v>85.5</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>21.6</v>
@@ -2600,30 +2590,30 @@
         <v>1.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>812</v>
+        <v>82</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2633,7 +2623,7 @@
         <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>25.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2649,19 +2639,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
+        <v>50.1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>311.8</v>
+        <v>318.4</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>235.6</v>
+        <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
@@ -2670,25 +2660,25 @@
         <v>6.8</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>67.90000000000001</v>
+      <c r="L27" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
@@ -2700,23 +2690,25 @@
         <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>31.4</v>
+        <v>16</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>28.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="X27" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1865.9</v>
+        <v>196.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2732,22 +2724,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>631</v>
+        <v>1621</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>35.2</v>
+        <v>33.2</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>464.6</v>
-      </c>
-      <c r="F28" s="3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>81.59999999999999</v>
+      <c r="G28" s="3" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2768,30 +2760,30 @@
         <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>32.1</v>
+        <v>803.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>29.4</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>43.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2800,9 +2792,7 @@
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>90.8</v>
-      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2822,11 +2812,11 @@
       <c r="D29" s="3" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <v>22.1</v>
+      <c r="E29" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>28.3</v>
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2835,13 +2825,13 @@
         <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>10</v>
+        <v>49.3</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2853,13 +2843,13 @@
         <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.1</v>
+        <v>41.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.5</v>
+        <v>83.5</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>14</v>
@@ -2871,22 +2861,22 @@
         <v>19</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>75.7</v>
+        <v>47.1</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>10.8</v>
+        <v>23009</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2902,28 +2892,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2181.9</v>
+        <v>2281.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>161.6</v>
+        <v>1561.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>726.5</v>
+        <v>714.5</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>181.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>139.8</v>
+        <v>23.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>118.9</v>
@@ -2941,22 +2931,22 @@
         <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>159.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>12.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -2965,13 +2955,13 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1190</v>
+        <v>110</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>13.6</v>
+        <v>106.9</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>42.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2987,7 +2977,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>856.4</v>
+        <v>236.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
@@ -2999,7 +2989,7 @@
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.8</v>
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -3007,11 +2997,11 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3035,7 +3025,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3072,10 +3062,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6144.4</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>0.8</v>
+        <v>61.1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
@@ -3084,25 +3074,25 @@
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>62.1</v>
+        <v>6.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>126</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1.2</v>
@@ -3111,12 +3101,12 @@
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3128,20 +3118,20 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="8" t="n">
         <v>28.3</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3157,31 +3147,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>613.7</v>
+        <v>122.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
@@ -3193,38 +3183,40 @@
         <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>61.7</v>
+      <c r="W33" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1455.4</v>
+        <v>149.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>103.9</v>
+        <v>43.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3240,7 +3232,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3846.3</v>
+        <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.8</v>
@@ -3252,10 +3244,10 @@
         <v>23.2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.8</v>
+        <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3266,17 +3258,17 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.4</v>
+      <c r="M34" s="8" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>42.2</v>
+        <v>22.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3284,11 +3276,11 @@
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>32.4</v>
+      <c r="R34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
@@ -3296,20 +3288,20 @@
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>89</v>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1860.6</v>
+        <v>1801.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3330,25 +3322,25 @@
       <c r="D35" s="3" t="n">
         <v>50.3</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
@@ -3358,18 +3350,16 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="R35" s="8" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3378,8 +3368,8 @@
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U35" s="8" t="n">
-        <v>11.1</v>
+      <c r="U35" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3391,11 +3381,9 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>19.2</v>
-      </c>
+        <v>2121.5</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3420,20 +3408,16 @@
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H36" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3441,10 +3425,10 @@
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3459,13 +3443,13 @@
         <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.4</v>
+        <v>2.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>822.1</v>
+      <c r="V36" s="3" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>13.6</v>
@@ -3474,10 +3458,10 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1498.8</v>
+        <v>1186</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>116.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3496,73 +3480,73 @@
         <v>2216.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>121.6</v>
+        <v>11810.6</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>168.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>11025.3</v>
+        <v>110.2</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>15.8</v>
+        <v>33.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1018</v>
+        <v>180</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>593.5</v>
+        <v>89.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>151.6</v>
+        <v>1151</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111.3</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>1315</v>
+        <v>1181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3578,9 +3562,9 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="D38" s="3" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>30.3</v>
       </c>
       <c r="E38" s="3" t="n">
@@ -3589,11 +3573,11 @@
       <c r="F38" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>19.2</v>
+      <c r="G38" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
@@ -3607,32 +3591,32 @@
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.2</v>
+        <v>27.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3665,71 +3649,71 @@
       <c r="C39" s="3" t="n">
         <v>914.6</v>
       </c>
-      <c r="D39" s="8" t="n">
-        <v>192.1</v>
+      <c r="D39" s="3" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1412.6</v>
+        <v>41.6</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>211.9</v>
+        <v>186.6</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>210.1</v>
+        <v>811</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>510.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>59.3</v>
+      <c r="Q39" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>96.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>28.8</v>
@@ -3748,25 +3732,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6471.6</v>
+        <v>641.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>91.7</v>
+        <v>90.7</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
@@ -3781,7 +3765,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3792,7 +3776,7 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="8" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3801,23 +3785,23 @@
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.2</v>
+      <c r="U40" s="3" t="n">
+        <v>84.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.1</v>
+      <c r="W40" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2216.3</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3836,28 +3820,28 @@
         <v>587.5</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>314.1</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>62.2</v>
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>1662.1</v>
+      <c r="G41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>18</v>
@@ -3869,10 +3853,10 @@
         <v>10.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>19.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
@@ -3884,24 +3868,24 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>22.2</v>
+        <v>122.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.6</v>
+        <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="X41" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y41" s="3" t="n">
-        <v>1828.4</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3918,23 +3902,23 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>12.1</v>
+      <c r="D42" s="3" t="n">
+        <v>31.1</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1.6</v>
+        <v>15.4</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>7.3</v>
@@ -3942,32 +3926,32 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -3975,14 +3959,14 @@
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>13</v>
+      <c r="W42" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -3999,10 +3983,10 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>5.6</v>
+        <v>534</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
@@ -4014,7 +3998,7 @@
         <v>4.1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>13.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4028,14 +4012,14 @@
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>921.6</v>
+        <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
@@ -4043,7 +4027,7 @@
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4053,13 +4037,13 @@
         <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4068,7 +4052,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.6</v>
+        <v>124.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4089,11 +4073,11 @@
       <c r="D44" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>222.9</v>
+      <c r="F44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>15.7</v>
@@ -4108,19 +4092,19 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4128,33 +4112,31 @@
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>7.8</v>
+        <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>12.8</v>
+        <v>112.3</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="8" t="n">
+      <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>12.8</v>
+      <c r="X44" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>1122.1</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4168,72 +4150,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>1801.1</v>
+      </c>
       <c r="D45" s="3" t="n">
-        <v>1555.1</v>
+        <v>185.1</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>411.9</v>
+        <v>91.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1102.1</v>
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>345</v>
+        <v>721.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>226.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>14.8</v>
+        <v>181.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1291.9</v>
+        <v>1281.8</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>102261.5</v>
+        <v>1226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>920.4</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>128.4</v>
+        <v>170</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>102.6</v>
-      </c>
+        <v>126.4</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="n">
-        <v>141.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>101</v>
+        <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.4</v>
+        <v>1222.9</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4250,30 +4232,32 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
+        <v>561.8</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>1</v>
+        <v>40.6</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>83</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -4284,7 +4268,7 @@
         <v>9.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>119.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4293,7 +4277,7 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
@@ -4302,22 +4286,22 @@
         <v>22.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>84.8</v>
+        <v>24</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>112.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -742,7 +742,7 @@
         <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>93.7</v>
+        <v>19.7</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>21.6</v>
@@ -751,7 +751,7 @@
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -760,7 +760,7 @@
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.1</v>
@@ -769,22 +769,22 @@
         <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>23.7</v>
+        <v>1.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>11.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>648.3</v>
+        <v>512.7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -833,19 +833,17 @@
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>15.5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
@@ -853,29 +851,29 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>84</v>
+      <c r="R5" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>16.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -894,7 +892,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>306.8</v>
+        <v>504.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>33.9</v>
@@ -906,55 +904,53 @@
         <v>22.3</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>100.8</v>
+        <v>140</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="8" t="n">
-        <v>91</v>
+      <c r="U6" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>4.1</v>
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
@@ -963,7 +959,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>20.2</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -984,17 +980,17 @@
       <c r="D7" s="3" t="n">
         <v>35.3</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1003,16 +999,16 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1023,32 +1019,32 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>3.2</v>
+      <c r="R7" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>13.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
+        <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>21.7</v>
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3</v>
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.3</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>16.3</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>2.8</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1064,10 +1060,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>285.1</v>
+        <v>485.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24.4</v>
+        <v>34.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>11</v>
@@ -1079,26 +1075,26 @@
         <v>23.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>81</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M8" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>3262</v>
+        <v>36.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1113,24 +1109,26 @@
         <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="Y8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="n">
+        <v>45.3</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1145,15 +1143,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19656.5</v>
+        <v>2636.1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1169.7</v>
+        <v>169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
+        <v>123.3</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1113.4</v>
+      </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
@@ -1161,43 +1161,43 @@
         <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>14.2</v>
+        <v>44.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>167.1</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>121.7</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>71.8</v>
+        <v>171.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>27.7</v>
+        <v>127.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1224.1</v>
+        <v>224.8</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
@@ -1206,10 +1206,10 @@
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1186.2</v>
+        <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>120.2</v>
@@ -1233,17 +1233,17 @@
       <c r="D10" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>10.7</v>
+      <c r="E10" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G10" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>2.3</v>
+      <c r="H10" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1263,7 +1263,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
@@ -1283,17 +1283,17 @@
       <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="3" t="n">
-        <v>13.9</v>
+      <c r="W10" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>87.8</v>
+        <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>1106.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>21.2</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1326,14 +1326,14 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>16.5</v>
+      <c r="I11" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
@@ -1345,7 +1345,7 @@
         <v>1.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>18.4</v>
@@ -1354,19 +1354,23 @@
         <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1387,13 +1391,13 @@
         <v>206.7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>51.3</v>
+        <v>31.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1406,7 +1410,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1415,43 +1419,43 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>11.8</v>
+        <v>20</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16</v>
+        <v>6.5</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>84</v>
+        <v>27</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>62.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1417</v>
+        <v>47</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1473,7 +1477,7 @@
         <v>34.3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15.9</v>
+        <v>42.4</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
@@ -1481,9 +1485,11 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="8" t="n">
+        <v>11.4</v>
+      </c>
       <c r="I13" s="3" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
@@ -1499,7 +1505,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>849</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
@@ -1508,7 +1514,7 @@
         <v>33.2</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1516,8 +1522,8 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>44</v>
+      <c r="U13" s="8" t="n">
+        <v>49</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
@@ -1529,10 +1535,10 @@
         <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0.2</v>
+        <v>28.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.5</v>
+        <v>25.4</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1548,13 +1554,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1572,37 +1578,35 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>4.5</v>
+      <c r="R14" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>73.8</v>
+        <v>7.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>36</v>
+      <c r="U14" s="8" t="n">
+        <v>236</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>27</v>
@@ -1611,13 +1615,13 @@
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1020.8</v>
+        <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>231.2</v>
+        <v>114.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1633,16 +1637,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2652.1</v>
+        <v>552.9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>15</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>16.3</v>
@@ -1662,42 +1666,46 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>148.8</v>
+        <v>418</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="8" t="n">
-        <v>0.8</v>
+      <c r="R15" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
+        <v>115.4</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>3.1</v>
+        <v>38</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>24</v>
+        <v>27.1</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>23.4</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1712,74 +1720,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>257.2</v>
+        <v>237.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8291.6</v>
+        <v>1291.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>21.8</v>
+        <v>76.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1118.2</v>
+        <v>2118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>97.3</v>
+        <v>397.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>136.2</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="n">
+        <v>880.9</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>22.1</v>
+        <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212.5</v>
+        <v>212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>184.7</v>
+        <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>173.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>128.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>22.8</v>
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>1145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1024.4</v>
+        <v>1224.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1795,31 +1805,31 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2313.4</v>
+        <v>315.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.9</v>
+        <v>21.9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>24.4</v>
+        <v>13.4</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18</v>
@@ -1828,10 +1838,10 @@
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1846,15 +1856,15 @@
         <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>27.4</v>
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>37.6</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>946.5</v>
-      </c>
-      <c r="W17" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1864,7 +1874,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>29.9</v>
+        <v>24.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1880,47 +1890,47 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.1</v>
+        <v>252.1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>20.5</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>15.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>13.5</v>
+      <c r="L18" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>137.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>80.59999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -1929,25 +1939,25 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.3</v>
+        <v>115.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V18" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>14.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>292.8</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1973,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.1</v>
+        <v>326.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
@@ -1980,15 +1990,17 @@
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+      <c r="I19" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>63.5</v>
+        <v>13.5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>7.9</v>
@@ -1997,7 +2009,7 @@
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
@@ -2005,7 +2017,7 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2017,20 +2029,20 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>96.90000000000001</v>
+      <c r="V19" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>292.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2046,16 +2058,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>322.8</v>
+        <v>322.5</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.1</v>
+        <v>34.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.8</v>
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>12.3</v>
+        <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2070,7 +2082,7 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>18</v>
@@ -2078,8 +2090,8 @@
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>19.1</v>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2097,22 +2109,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>44.8</v>
+        <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2137,16 +2149,16 @@
         <v>30.9</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2155,19 +2167,19 @@
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
@@ -2182,16 +2194,16 @@
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>17.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>86.3</v>
+      <c r="V21" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>0.4</v>
+        <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
@@ -2200,7 +2212,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>44.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2216,7 +2228,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>936.3</v>
+        <v>536.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
@@ -2236,24 +2248,22 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -2267,19 +2277,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
+        <v>114.9</v>
       </c>
       <c r="U22" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2307,10 +2317,10 @@
         <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1117.1</v>
+        <v>117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
@@ -2328,28 +2338,26 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.9</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1272</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>23.5</v>
-      </c>
+        <v>154.4</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>368.6</v>
+        <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2358,19 +2366,19 @@
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.6</v>
+        <v>130.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>68.8</v>
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2386,47 +2394,49 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>503.5</v>
+        <v>509.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>2.2</v>
+      <c r="H24" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>24.6</v>
+        <v>294.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>20.9</v>
+        <v>30.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>14.7</v>
@@ -2444,7 +2454,7 @@
         <v>26.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
@@ -2469,13 +2479,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
+        <v>45.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>24.8</v>
@@ -2492,7 +2502,7 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2502,43 +2512,43 @@
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>401</v>
+        <v>40</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="Q25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="S25" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S25" s="8" t="n">
-        <v>37.3</v>
-      </c>
       <c r="T25" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>12.8</v>
+        <v>18.3</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y25" s="3" t="n">
-        <v>41.6</v>
-      </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>457.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2559,16 +2569,16 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="H26" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2580,10 +2590,10 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M26" s="8" t="n">
+      <c r="L26" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2596,7 +2606,7 @@
         <v>8.6</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>99.3</v>
+        <v>29.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>14.2</v>
@@ -2607,23 +2617,23 @@
       <c r="T26" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="8" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="W26" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.1</v>
+        <v>25</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2639,10 +2649,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>50.1</v>
+        <v>550.1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>318.4</v>
+        <v>31.8</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>15.2</v>
@@ -2657,9 +2667,9 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
@@ -2672,43 +2682,43 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>17.4</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>37.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>0.1</v>
+        <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>196.5</v>
+        <v>26.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2724,31 +2734,31 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
+        <v>621</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="F28" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G28" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
@@ -2757,42 +2767,44 @@
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P28" s="8" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>803.9</v>
+        <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>598.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2807,7 +2819,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.8</v>
+        <v>624.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>34.4</v>
@@ -2815,8 +2827,8 @@
       <c r="E29" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>23.3</v>
+      <c r="F29" s="8" t="n">
+        <v>38.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2828,10 +2840,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>181.1</v>
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2849,7 +2861,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>14</v>
@@ -2860,14 +2872,14 @@
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="8" t="n">
         <v>47.1</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>6.9</v>
@@ -2876,7 +2888,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>23009</v>
+        <v>30.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2892,13 +2904,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2281.9</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1561.6</v>
+        <v>161.6</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>118</v>
@@ -2907,16 +2919,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>237</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.8</v>
+        <v>135.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>118.9</v>
+        <v>18.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
@@ -2928,22 +2940,22 @@
         <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>155.1</v>
+        <v>153.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.9</v>
+        <v>20.9</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
@@ -2952,16 +2964,14 @@
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>110</v>
-      </c>
+        <v>66.8</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>106.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.8</v>
+        <v>122.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2977,7 +2987,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
+        <v>336.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
@@ -2997,17 +3007,15 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>110.1</v>
+      <c r="M31" s="8" t="n">
+        <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0.8</v>
@@ -3015,7 +3023,7 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
@@ -3025,7 +3033,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3043,10 +3051,10 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.2</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3062,10 +3070,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>61.1</v>
+        <v>208.6</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.8</v>
+        <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
@@ -3076,9 +3084,7 @@
       <c r="G32" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -3086,22 +3092,22 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>1.4</v>
+        <v>10</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>33.6</v>
@@ -3113,25 +3119,23 @@
         <v>14.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>19</v>
+        <v>1141.1</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>28.3</v>
+        <v>484.1</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>90.8</v>
       </c>
       <c r="W32" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>13.7</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3147,25 +3151,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>122.5</v>
+        <v>443.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3173,14 +3177,14 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>41</v>
@@ -3191,7 +3195,7 @@
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3201,22 +3205,22 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>93.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>149.2</v>
+        <v>1420.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>43.2</v>
+        <v>113.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3237,20 +3241,20 @@
       <c r="D34" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>5.6</v>
+      <c r="E34" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3261,11 +3265,11 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>81.40000000000001</v>
+      <c r="M34" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>22.2</v>
@@ -3277,31 +3281,31 @@
         <v>19</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+        <v>12.7</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1801.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3317,10 +3321,10 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>439.9</v>
+        <v>433.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.3</v>
+        <v>30.3</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>17</v>
@@ -3328,20 +3332,20 @@
       <c r="F35" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>14.3</v>
+        <v>47.1</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3350,7 +3354,7 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>1.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
@@ -3358,18 +3362,20 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q35" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>58.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>23.4</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3381,9 +3387,11 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>2121.5</v>
-      </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3401,22 +3409,26 @@
         <v>341.3</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+        <v>45.4</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="F36" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H36" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3428,7 +3440,7 @@
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3440,28 +3452,28 @@
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.4</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>10.6</v>
+      <c r="X36" s="8" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1186</v>
+        <v>146.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3480,46 +3492,46 @@
         <v>2216.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>11810.6</v>
+        <v>131.6</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>168.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>110.2</v>
+        <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>33.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>3.6</v>
+        <v>36.1</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>3.2</v>
+        <v>153.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.7</v>
+        <v>44.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1240.2</v>
+        <v>2409.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>89.3</v>
+        <v>359.5</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.5</v>
+        <v>13.3</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>82.59999999999999</v>
@@ -3528,25 +3540,23 @@
         <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1151</v>
+        <v>171.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>114.1</v>
+        <v>1141.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>49.8</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>1181.2</v>
+        <v>188.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3562,63 +3572,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>442.2</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E38" s="3" t="n">
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
+      <c r="G38" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.2</v>
+        <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>27.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="Q38" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q38" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
@@ -3647,40 +3655,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>914.6</v>
+        <v>5914.6</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>41.6</v>
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>186.6</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>811</v>
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.9</v>
+        <v>17.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21</v>
@@ -3698,7 +3706,7 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>29.4</v>
@@ -3709,14 +3717,14 @@
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>28.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3732,10 +3740,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>641.4</v>
+        <v>617.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>90.7</v>
+        <v>30.7</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>14.7</v>
@@ -3750,25 +3758,25 @@
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.1</v>
+        <v>21.7</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3776,32 +3784,32 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>26</v>
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>268</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.1</v>
+        <v>223.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3823,16 +3831,16 @@
         <v>31.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13</v>
+      <c r="H41" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3846,14 +3854,14 @@
       <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>11.9</v>
+      <c r="M41" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="P41" s="8" t="n">
         <v>10.8</v>
@@ -3868,23 +3876,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="8" t="n">
         <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X41" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y41" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>128.9</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>0.2</v>
+        <v>26.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3903,16 +3913,16 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>31.1</v>
+        <v>39.2</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>12</v>
@@ -3921,7 +3931,7 @@
         <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
@@ -3929,17 +3939,17 @@
       <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>26.4</v>
@@ -3951,24 +3961,26 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.7</v>
+        <v>128.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>1392</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3983,10 +3995,10 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>534</v>
+        <v>234</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
@@ -3995,10 +4007,10 @@
         <v>23.5</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>4.1</v>
+        <v>14.1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>83.40000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4007,7 +4019,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
@@ -4016,13 +4028,13 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
@@ -4034,16 +4046,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="U43" s="3" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="U43" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4052,7 +4064,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>124.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4068,7 +4080,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.7</v>
@@ -4076,7 +4088,7 @@
       <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4092,37 +4104,37 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P44" s="3" t="n">
+        <v>644</v>
+      </c>
+      <c r="P44" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>112.3</v>
+        <v>119.2</v>
       </c>
       <c r="U44" s="8" t="n">
-        <v>22.8</v>
+        <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
@@ -4130,13 +4142,15 @@
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>0.1</v>
+      <c r="X44" s="8" t="n">
+        <v>227.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>290.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>112.4</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4151,72 +4165,70 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1801.1</v>
+        <v>2312.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>185.1</v>
+        <v>188.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>91.7</v>
+        <v>24.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1122.1</v>
+        <v>113.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>910.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.7</v>
+        <v>7194.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>721.1</v>
+        <v>85</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>181.2</v>
+        <v>12.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1281.8</v>
+        <v>101.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>1202.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27.1</v>
+        <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1226.5</v>
+        <v>226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
+        <v>2908.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>81.5</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>180</v>
+        <v>182.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="U45" s="3" t="inlineStr"/>
+        <v>136.9</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>182.6</v>
+      </c>
       <c r="V45" s="3" t="n">
-        <v>144.2</v>
+        <v>146.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>28.8</v>
+        <v>286.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>1222.9</v>
-      </c>
+        <v>164.7</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4232,43 +4244,41 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>561.8</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="E46" s="8" t="n">
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>83</v>
+        <v>22.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>80.8</v>
+        <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4277,31 +4287,31 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>39</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>24</v>
+      <c r="U46" s="8" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>84.8</v>
       </c>
       <c r="W46" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>112.6</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -742,7 +733,7 @@
         <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>21.6</v>
@@ -754,22 +745,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -780,11 +771,11 @@
       <c r="Q4" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -809,7 +800,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
+        <v>12.7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
@@ -817,10 +808,10 @@
       <c r="E5" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -833,17 +824,17 @@
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
@@ -860,7 +851,7 @@
       <c r="T5" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
@@ -870,10 +861,10 @@
         <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>16.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -903,8 +894,8 @@
       <c r="F6" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>23.9</v>
+      <c r="G6" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -926,15 +917,15 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -959,7 +950,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       <c r="F7" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -999,7 +990,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1008,10 +999,10 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
@@ -1019,11 +1010,11 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
@@ -1038,10 +1029,10 @@
         <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>33.4</v>
@@ -1080,7 +1071,7 @@
       <c r="I8" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="K8" s="3" t="n">
@@ -1102,7 +1093,7 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1112,12 +1103,12 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.7</v>
+        <v>51.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1143,16 +1134,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636.1</v>
+        <v>2656</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>123.3</v>
+        <v>53.3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1113.4</v>
+        <v>111.4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
@@ -1167,10 +1158,10 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>167.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>32.5</v>
@@ -1179,40 +1170,40 @@
         <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>165</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>171.8</v>
+        <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.8</v>
+        <v>224.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>169.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>120.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1231,19 +1222,19 @@
         <v>531.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>10.2</v>
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>47.8</v>
+      <c r="H10" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1283,14 +1274,14 @@
       <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="8" t="n">
-        <v>19.9</v>
+      <c r="W10" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1106.2</v>
+        <v>106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>21.2</v>
@@ -1309,16 +1300,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
+        <v>27.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>83.8</v>
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1326,14 +1317,14 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>46.9</v>
+      <c r="I11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
@@ -1342,7 +1333,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1362,14 +1353,14 @@
       <c r="T11" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>31</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>14</v>
+      <c r="W11" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1394,10 +1385,10 @@
         <v>31.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1419,13 +1410,13 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="8" t="n">
-        <v>20</v>
+      <c r="P12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.3</v>
@@ -1439,17 +1430,17 @@
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>29.2</v>
+      <c r="U12" s="3" t="n">
+        <v>39.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>27</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>2.3</v>
+        <v>15.1</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>47</v>
@@ -1485,7 +1476,7 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1513,8 +1504,8 @@
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.8</v>
+      <c r="R13" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1522,8 +1513,8 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>49</v>
+      <c r="U13" s="3" t="n">
+        <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
@@ -1560,7 +1551,7 @@
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1583,8 +1574,8 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>22</v>
+      <c r="M14" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
@@ -1593,10 +1584,10 @@
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1605,8 +1596,8 @@
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="8" t="n">
-        <v>236</v>
+      <c r="U14" s="3" t="n">
+        <v>36</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>27</v>
@@ -1615,13 +1606,13 @@
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>114.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1637,18 +1628,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.9</v>
+        <v>552.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1666,27 +1657,27 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>418</v>
+        <v>48</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
+        <v>15.4</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>38</v>
@@ -1720,40 +1711,40 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.7</v>
+        <v>257.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1291.6</v>
+        <v>159.6</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>76.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2118.2</v>
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>397.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>136.2</v>
+        <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>880.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>212.5</v>
@@ -1765,31 +1756,31 @@
         <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>173.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.3</v>
+        <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>72.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1145.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1224.4</v>
+        <v>124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1805,10 +1796,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
+        <v>15.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13.4</v>
@@ -1816,14 +1807,14 @@
       <c r="F17" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
@@ -1834,11 +1825,11 @@
       <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1864,11 +1855,11 @@
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>29.2</v>
@@ -1890,12 +1881,12 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>252.1</v>
+        <v>552.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1914,23 +1905,23 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>18.5</v>
+      <c r="L18" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>137.5</v>
+        <v>27.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>29.1</v>
+      <c r="Q18" s="3" t="n">
+        <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -1939,16 +1930,16 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
+        <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>22.2</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>84.40000000000001</v>
+      <c r="W18" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>8.4</v>
@@ -1957,7 +1948,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1964,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>526.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
@@ -1993,8 +1984,8 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <v>20.6</v>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
@@ -2009,7 +2000,7 @@
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
@@ -2029,14 +2020,14 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2082,16 +2073,16 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2117,7 +2108,7 @@
       <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2127,7 +2118,7 @@
         <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+        <v>18.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2143,12 +2134,12 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>42.2</v>
+        <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
@@ -2158,7 +2149,7 @@
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2179,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
@@ -2194,7 +2185,7 @@
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
@@ -2248,16 +2239,16 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="8" t="n">
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2277,13 +2268,13 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
@@ -2311,7 +2302,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2517.5</v>
+        <v>2547.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>160.3</v>
@@ -2326,13 +2317,13 @@
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
+        <v>57.2</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>3.3</v>
@@ -2344,13 +2335,13 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>154.4</v>
@@ -2369,10 +2360,10 @@
         <v>130.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
@@ -2421,7 +2412,7 @@
         <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
@@ -2430,7 +2421,7 @@
         <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>294.6</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2460,10 +2451,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2479,18 +2470,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.5</v>
+        <v>455.5</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2508,7 +2499,7 @@
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2517,38 +2508,38 @@
       <c r="O25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>14.8</v>
+      <c r="P25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>26.2</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>457.3</v>
+        <v>45.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2569,17 +2560,17 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.8</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>7.3</v>
@@ -2597,10 +2588,10 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2612,25 +2603,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="U26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>25</v>
@@ -2657,7 +2648,7 @@
       <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2667,7 +2658,7 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>10.4</v>
@@ -2693,14 +2684,14 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>37.4</v>
@@ -2712,10 +2703,10 @@
         <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>26.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>26.3</v>
@@ -2739,23 +2730,23 @@
       <c r="D28" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>18.1</v>
+      <c r="G28" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2767,12 +2758,12 @@
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P28" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
@@ -2782,13 +2773,13 @@
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>598.4</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>27.7</v>
@@ -2827,8 +2818,8 @@
       <c r="E29" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>38.3</v>
+      <c r="F29" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2863,16 +2854,16 @@
       <c r="Q29" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>47.1</v>
       </c>
       <c r="V29" s="3" t="n">
@@ -2888,7 +2879,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2922,19 +2913,19 @@
         <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>135.8</v>
+        <v>25.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>30.6</v>
+        <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
@@ -2943,19 +2934,19 @@
         <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>91.7</v>
+        <v>51.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
@@ -2987,7 +2978,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>336.4</v>
+        <v>556.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
@@ -3007,14 +2998,14 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3023,7 +3014,7 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
@@ -3033,7 +3024,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3051,7 +3042,7 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>21.6</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>1.8</v>
@@ -3070,7 +3061,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>208.6</v>
+        <v>611.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3092,16 +3083,16 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3116,16 +3107,16 @@
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1141.1</v>
+        <v>15.1</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>90.8</v>
+        <v>9</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>28.5</v>
@@ -3151,25 +3142,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>443.7</v>
+        <v>43.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="8" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F33" s="8" t="n">
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3177,7 +3168,7 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3195,7 +3186,7 @@
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3204,23 +3195,23 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="U33" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X33" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3247,14 +3238,14 @@
       <c r="F34" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3269,10 +3260,10 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>22.2</v>
+        <v>52.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3287,25 +3278,25 @@
         <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25.9</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+      <c r="X34" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3332,17 +3323,17 @@
       <c r="F35" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>47.1</v>
@@ -3354,22 +3345,22 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>58.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
@@ -3384,7 +3375,7 @@
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0.2</v>
@@ -3417,8 +3408,8 @@
       <c r="F36" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G36" s="8" t="n">
-        <v>4.8</v>
+      <c r="G36" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
@@ -3440,7 +3431,7 @@
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3458,22 +3449,22 @@
         <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>146.6</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>16.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3492,10 +3483,10 @@
         <v>2216.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>131.6</v>
+        <v>151.6</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>110.3</v>
@@ -3516,47 +3507,47 @@
         <v>36.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>153.2</v>
+        <v>53.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>2409.2</v>
+        <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>359.5</v>
+        <v>59.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>13.3</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>171.6</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1141.1</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>188.2</v>
+        <v>187.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3575,28 +3566,28 @@
         <v>443.3</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
@@ -3606,10 +3597,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>26.7</v>
@@ -3621,12 +3612,12 @@
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="8" t="n">
+      <c r="V38" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
@@ -3655,7 +3646,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5914.6</v>
+        <v>514.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>29.2</v>
@@ -3663,32 +3654,32 @@
       <c r="E39" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>158</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21</v>
@@ -3706,9 +3697,9 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U39" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U39" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="V39" s="3" t="n">
@@ -3740,7 +3731,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
+        <v>17.1</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>30.7</v>
@@ -3751,10 +3742,10 @@
       <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3773,10 +3764,10 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>21.7</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3794,22 +3785,22 @@
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v>268</v>
+        <v>34.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>318</v>
+        <v>30</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>223.6</v>
+        <v>23.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3833,14 +3824,14 @@
       <c r="E41" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>53</v>
+      <c r="H41" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3851,19 +3842,19 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L41" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="8" t="n">
+      <c r="P41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
@@ -3878,7 +3869,7 @@
       <c r="T41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="U41" s="8" t="n">
+      <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
@@ -3888,10 +3879,10 @@
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.9</v>
+        <v>28.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>26.4</v>
@@ -3913,15 +3904,15 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>39.2</v>
+        <v>31.2</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3936,7 +3927,7 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3961,7 +3952,7 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>128.7</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -3970,16 +3961,16 @@
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1392</v>
+        <v>52</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3995,7 +3986,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>234</v>
+        <v>554</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>30.5</v>
@@ -4006,10 +3997,10 @@
       <c r="F43" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4019,7 +4010,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
@@ -4028,13 +4019,13 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>31.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
@@ -4046,16 +4037,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="U43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4088,7 +4079,7 @@
       <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4104,7 +4095,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
@@ -4116,24 +4107,24 @@
         <v>1.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>644</v>
-      </c>
-      <c r="P44" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>87.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="U44" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
@@ -4142,14 +4133,14 @@
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>227.9</v>
+      <c r="X44" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>290.8</v>
+        <v>50.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4165,25 +4156,25 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2312.2</v>
+        <v>312.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>188.7</v>
+        <v>185.7</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>910.8</v>
+        <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>7194.9</v>
+        <v>21.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
@@ -4192,41 +4183,41 @@
         <v>12.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>101.9</v>
+        <v>101.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1202.9</v>
+        <v>222.1</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>296.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2908.4</v>
+        <v>58.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>182.8</v>
+        <v>23.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>136.9</v>
+        <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>182.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>146.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>286.2</v>
+        <v>22.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>164.7</v>
+        <v>54.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4246,39 +4237,41 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>70.59999999999999</v>
+      <c r="D46" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4287,31 +4280,31 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S46" s="8" t="n">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>16.8</v>
+      <c r="U46" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -760,7 +760,7 @@
         <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>12.7</v>
+        <v>512.7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
@@ -849,7 +849,7 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>46.8</v>
@@ -999,10 +999,10 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
@@ -1103,7 +1103,7 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>51.7</v>
+        <v>31.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
@@ -1140,7 +1140,7 @@
         <v>169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>111.4</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.9</v>
+        <v>427.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
@@ -1333,7 +1333,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>12.7</v>
+        <v>1.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
@@ -1655,14 +1655,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>26.2</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1717,7 +1717,7 @@
         <v>159.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>76.8</v>
+        <v>26.8</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>118.2</v>
@@ -1732,7 +1732,7 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>36.2</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>1.7</v>
@@ -1744,10 +1744,10 @@
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>218.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
@@ -1768,10 +1768,10 @@
         <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>72.5</v>
+        <v>12.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>15.4</v>
+        <v>515.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>31.9</v>
@@ -1808,7 +1808,7 @@
         <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>552.1</v>
+        <v>352.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.9</v>
@@ -1912,10 +1912,10 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
@@ -1933,7 +1933,7 @@
         <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>22.2</v>
+        <v>40.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
@@ -2027,7 +2027,7 @@
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2058,7 +2058,7 @@
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>20.3</v>
+        <v>24.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2252,7 +2252,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
@@ -2308,7 +2308,7 @@
         <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>117.1</v>
@@ -2317,13 +2317,13 @@
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>3.3</v>
@@ -2335,7 +2335,7 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>273</v>
@@ -2512,7 +2512,7 @@
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2564,10 +2564,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2588,7 +2588,7 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>22</v>
@@ -2673,10 +2673,10 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2776,10 +2776,10 @@
         <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>19.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
+        <v>13.4</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>27.7</v>
@@ -2822,7 +2822,7 @@
         <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2843,7 +2843,7 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
+        <v>271.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>161.6</v>
@@ -2916,7 +2916,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>25.8</v>
+        <v>35.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>10.9</v>
@@ -2943,7 +2943,7 @@
         <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>72.59999999999999</v>
@@ -3009,7 +3009,7 @@
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
@@ -3024,7 +3024,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3042,10 +3042,10 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>21.6</v>
+        <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>15.1</v>
+        <v>1.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>43.7</v>
+        <v>243.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
@@ -3196,7 +3196,7 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>23.4</v>
+        <v>13.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3245,7 +3245,7 @@
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3260,10 +3260,10 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>32.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3293,10 +3293,10 @@
         <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>9.6</v>
@@ -3406,7 +3406,7 @@
         <v>11.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>14.3</v>
@@ -3461,7 +3461,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>40</v>
+        <v>20.2</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3495,7 +3495,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.8</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3519,7 +3519,7 @@
         <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.3</v>
+        <v>39.3</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>133.5</v>
@@ -3540,7 +3540,7 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3586,7 +3586,9 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -3594,7 +3596,7 @@
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
@@ -3612,7 +3614,7 @@
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10.3</v>
+        <v>30.3</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>26.9</v>
@@ -3682,7 +3684,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3731,7 +3733,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>17.1</v>
+        <v>617.1</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>30.7</v>
@@ -3764,7 +3766,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>51</v>
@@ -3849,7 +3851,7 @@
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
@@ -3961,10 +3963,10 @@
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4010,7 +4012,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
@@ -4046,7 +4048,7 @@
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4095,7 +4097,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
@@ -4104,10 +4106,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4122,7 +4124,7 @@
         <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>32.8</v>
@@ -4156,7 +4158,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>312.2</v>
+        <v>3312.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>185.7</v>
@@ -4165,7 +4167,7 @@
         <v>24.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>91.8</v>
@@ -4177,7 +4179,7 @@
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.3</v>
+        <v>32.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>12.2</v>
@@ -4186,10 +4188,10 @@
         <v>101.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>222.1</v>
+        <v>224</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>2.7</v>
+        <v>27</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4214,10 +4216,10 @@
         <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>22.8</v>
+        <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>54.7</v>
+        <v>186.2</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4238,7 +4240,7 @@
         <v>551.8</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>20.6</v>
+        <v>30.6</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>15.3</v>
@@ -4247,7 +4249,7 @@
         <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
@@ -4268,7 +4270,7 @@
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>9.6</v>
+        <v>2.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>49.4</v>
@@ -4295,13 +4297,13 @@
         <v>24</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>27.1</v>
+        <v>31.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -760,7 +760,7 @@
         <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -849,7 +849,7 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>46.8</v>
@@ -999,10 +999,10 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36.2</v>
+        <v>26.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1103,7 +1103,7 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>31.7</v>
+        <v>51.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
@@ -1275,7 +1275,7 @@
         <v>27.9</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
@@ -1303,7 +1303,7 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
@@ -1333,7 +1333,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>31.1</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>149.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
@@ -1655,14 +1655,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>26.2</v>
+        <v>48</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1717,7 +1717,7 @@
         <v>159.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>26.8</v>
+        <v>76.8</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>118.2</v>
@@ -1732,7 +1732,7 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>1.7</v>
@@ -1771,7 +1771,7 @@
         <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.5</v>
+        <v>72.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>515.4</v>
+        <v>55.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>23.6</v>
@@ -1820,7 +1820,7 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18</v>
@@ -1829,7 +1829,7 @@
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>352.1</v>
+        <v>552.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.9</v>
@@ -1912,10 +1912,10 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>37.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
@@ -2027,7 +2027,7 @@
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2058,7 +2058,7 @@
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.3</v>
+        <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2252,7 +2252,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
@@ -2308,7 +2308,7 @@
         <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>73.5</v>
+        <v>78.5</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>117.1</v>
@@ -2317,13 +2317,13 @@
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>22.2</v>
+        <v>69</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
+        <v>57.2</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>3.3</v>
@@ -2335,10 +2335,10 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>41.3</v>
@@ -2503,7 +2503,7 @@
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.9</v>
+        <v>9.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>40</v>
@@ -2512,7 +2512,7 @@
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2564,10 +2564,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2588,10 +2588,10 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2673,10 +2673,10 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2740,7 +2740,7 @@
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>20.4</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2776,10 +2776,10 @@
         <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>27.7</v>
@@ -2843,7 +2843,7 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>271.9</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>161.6</v>
@@ -2916,7 +2916,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>10.9</v>
@@ -2949,7 +2949,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>19.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -3009,7 +3009,7 @@
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
@@ -3024,7 +3024,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3045,7 +3045,7 @@
         <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>611.1</v>
+        <v>61.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3092,7 +3092,7 @@
         <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3110,7 +3110,7 @@
         <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>243.7</v>
+        <v>43.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
@@ -3196,7 +3196,7 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>13.4</v>
+        <v>123.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3208,7 +3208,7 @@
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>22.2</v>
+        <v>42.2</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>13.9</v>
@@ -3260,7 +3260,7 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>32.2</v>
@@ -3296,7 +3296,7 @@
         <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0.2</v>
+        <v>33.2</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>19.2</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>341.3</v>
+        <v>34.1</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>45.4</v>
@@ -3461,7 +3461,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>20.2</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2216.6</v>
+        <v>221.6</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>151.6</v>
@@ -3495,7 +3495,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3540,7 +3540,7 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3586,9 +3586,7 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -3596,7 +3594,7 @@
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
@@ -3660,7 +3658,7 @@
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>11.2</v>
@@ -3681,7 +3679,7 @@
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>31</v>
@@ -3766,7 +3764,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>51</v>
@@ -3784,7 +3782,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3851,7 +3849,7 @@
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
@@ -3881,7 +3879,7 @@
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>28.4</v>
@@ -3963,10 +3961,10 @@
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>123</v>
+        <v>813</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4021,7 +4019,7 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>31.5</v>
@@ -4073,7 +4071,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
+        <v>58</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.7</v>
@@ -4106,7 +4104,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>18.1</v>
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>44</v>
@@ -4124,7 +4122,7 @@
         <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>32.8</v>
@@ -4136,7 +4134,7 @@
         <v>14.7</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>50.8</v>
@@ -4158,7 +4156,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3312.2</v>
+        <v>331.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>185.7</v>
@@ -4173,13 +4171,13 @@
         <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>32.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>12.2</v>
@@ -4188,10 +4186,10 @@
         <v>101.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27</v>
+        <v>57.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4210,7 +4208,7 @@
         <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>182.6</v>
+        <v>185.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>144.2</v>
@@ -4219,7 +4217,7 @@
         <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>186.2</v>
+        <v>64.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4261,7 +4259,7 @@
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
@@ -4270,7 +4268,7 @@
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>49.4</v>
@@ -4297,13 +4295,13 @@
         <v>24</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>31.1</v>
+        <v>21.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>
